--- a/dados/gerencial/consolidado_gerencial_2024.xlsx
+++ b/dados/gerencial/consolidado_gerencial_2024.xlsx
@@ -491,19 +491,19 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>398</v>
+        <v>432</v>
       </c>
       <c r="D4" t="n">
         <v>197</v>
       </c>
       <c r="E4" t="n">
-        <v>2242879.48</v>
+        <v>2235105.74</v>
       </c>
       <c r="F4" t="n">
-        <v>1475472.21</v>
+        <v>1467738.59</v>
       </c>
       <c r="G4" s="3" t="n">
-        <v>45334</v>
+        <v>45331</v>
       </c>
     </row>
     <row r="5">
@@ -516,19 +516,19 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="D5" t="n">
         <v>55</v>
       </c>
       <c r="E5" t="n">
-        <v>1554089.42</v>
+        <v>1577115.49</v>
       </c>
       <c r="F5" t="n">
-        <v>934234.11</v>
+        <v>1030636.77</v>
       </c>
       <c r="G5" s="3" t="n">
-        <v>45330</v>
+        <v>45334</v>
       </c>
     </row>
     <row r="6">
@@ -541,19 +541,19 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="D6" t="n">
         <v>16</v>
       </c>
       <c r="E6" t="n">
-        <v>118185.37</v>
+        <v>123803.92</v>
       </c>
       <c r="F6" t="n">
-        <v>92407.75</v>
+        <v>86117.74000000001</v>
       </c>
       <c r="G6" s="3" t="n">
-        <v>45334</v>
+        <v>45330</v>
       </c>
     </row>
     <row r="7">
@@ -566,19 +566,19 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>333</v>
+        <v>361</v>
       </c>
       <c r="D7" t="n">
         <v>155</v>
       </c>
       <c r="E7" t="n">
-        <v>2038363.63</v>
+        <v>2059222.58</v>
       </c>
       <c r="F7" t="n">
-        <v>1306881.42</v>
+        <v>1159430.67</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>45362</v>
+        <v>45363</v>
       </c>
     </row>
     <row r="8">
@@ -591,19 +591,19 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>259</v>
+        <v>264</v>
       </c>
       <c r="D8" t="n">
         <v>55</v>
       </c>
       <c r="E8" t="n">
-        <v>1555292.72</v>
+        <v>1571468.38</v>
       </c>
       <c r="F8" t="n">
-        <v>889386.87</v>
+        <v>976500.61</v>
       </c>
       <c r="G8" s="3" t="n">
-        <v>45365</v>
+        <v>45363</v>
       </c>
     </row>
     <row r="9">
@@ -616,19 +616,19 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36</v>
+        <v>38</v>
       </c>
       <c r="D9" t="n">
         <v>12</v>
       </c>
       <c r="E9" t="n">
-        <v>202679.82</v>
+        <v>180713.92</v>
       </c>
       <c r="F9" t="n">
-        <v>140071.14</v>
+        <v>140453.81</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>45366</v>
+        <v>45359</v>
       </c>
     </row>
     <row r="10">
@@ -641,19 +641,19 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>326</v>
+        <v>354</v>
       </c>
       <c r="D10" t="n">
         <v>185</v>
       </c>
       <c r="E10" t="n">
-        <v>1744430.21</v>
+        <v>1789752.15</v>
       </c>
       <c r="F10" t="n">
-        <v>1189415.24</v>
+        <v>1205526</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>45392</v>
+        <v>45393</v>
       </c>
     </row>
     <row r="11">
@@ -666,19 +666,19 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="D11" t="n">
         <v>53</v>
       </c>
       <c r="E11" t="n">
-        <v>1563290.15</v>
+        <v>1574300.27</v>
       </c>
       <c r="F11" t="n">
-        <v>923993.08</v>
+        <v>918152.63</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>45392</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="12">
@@ -691,19 +691,19 @@
         </is>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D12" t="n">
         <v>14</v>
       </c>
       <c r="E12" t="n">
-        <v>203859.6</v>
+        <v>222721.85</v>
       </c>
       <c r="F12" t="n">
-        <v>141508.17</v>
+        <v>156847.48</v>
       </c>
       <c r="G12" s="3" t="n">
-        <v>45394</v>
+        <v>45397</v>
       </c>
     </row>
     <row r="13">
@@ -716,19 +716,19 @@
         </is>
       </c>
       <c r="C13" t="n">
-        <v>338</v>
+        <v>373</v>
       </c>
       <c r="D13" t="n">
         <v>227</v>
       </c>
       <c r="E13" t="n">
-        <v>1907086.2</v>
+        <v>1933526.97</v>
       </c>
       <c r="F13" t="n">
-        <v>1256899.07</v>
+        <v>1283077.05</v>
       </c>
       <c r="G13" s="3" t="n">
-        <v>45426</v>
+        <v>45427</v>
       </c>
     </row>
     <row r="14">
@@ -741,16 +741,16 @@
         </is>
       </c>
       <c r="C14" t="n">
-        <v>265</v>
+        <v>286</v>
       </c>
       <c r="D14" t="n">
         <v>50</v>
       </c>
       <c r="E14" t="n">
-        <v>1573480.07</v>
+        <v>1412725.8</v>
       </c>
       <c r="F14" t="n">
-        <v>931271.1800000001</v>
+        <v>1019531.02</v>
       </c>
       <c r="G14" s="3" t="n">
         <v>45425</v>
@@ -766,16 +766,16 @@
         </is>
       </c>
       <c r="C15" t="n">
-        <v>48</v>
+        <v>42</v>
       </c>
       <c r="D15" t="n">
         <v>17</v>
       </c>
       <c r="E15" t="n">
-        <v>234610.86</v>
+        <v>241552.66</v>
       </c>
       <c r="F15" t="n">
-        <v>147493.59</v>
+        <v>152481.17</v>
       </c>
       <c r="G15" s="3" t="n">
         <v>45420</v>
@@ -791,19 +791,19 @@
         </is>
       </c>
       <c r="C16" t="n">
-        <v>348</v>
+        <v>384</v>
       </c>
       <c r="D16" t="n">
         <v>212</v>
       </c>
       <c r="E16" t="n">
-        <v>2232135.9</v>
+        <v>2001581.04</v>
       </c>
       <c r="F16" t="n">
-        <v>1326029.86</v>
+        <v>1484328.05</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>45453</v>
+        <v>45460</v>
       </c>
     </row>
     <row r="17">
@@ -822,13 +822,13 @@
         <v>73</v>
       </c>
       <c r="E17" t="n">
-        <v>1484559.12</v>
+        <v>1452687.68</v>
       </c>
       <c r="F17" t="n">
-        <v>1081663.5</v>
+        <v>1075584.71</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>45453</v>
+        <v>45457</v>
       </c>
     </row>
     <row r="18">
@@ -841,19 +841,19 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>44</v>
+        <v>46</v>
       </c>
       <c r="D18" t="n">
         <v>23</v>
       </c>
       <c r="E18" t="n">
-        <v>224144.92</v>
+        <v>245618.27</v>
       </c>
       <c r="F18" t="n">
-        <v>161650.85</v>
+        <v>159296.26</v>
       </c>
       <c r="G18" s="3" t="n">
-        <v>45456</v>
+        <v>45453</v>
       </c>
     </row>
     <row r="19">
@@ -866,19 +866,19 @@
         </is>
       </c>
       <c r="C19" t="n">
-        <v>388</v>
+        <v>391</v>
       </c>
       <c r="D19" t="n">
         <v>192</v>
       </c>
       <c r="E19" t="n">
-        <v>2464501.1</v>
+        <v>2192698.27</v>
       </c>
       <c r="F19" t="n">
-        <v>1445935.71</v>
+        <v>1445976.49</v>
       </c>
       <c r="G19" s="3" t="n">
-        <v>45481</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="20">
@@ -891,19 +891,19 @@
         </is>
       </c>
       <c r="C20" t="n">
-        <v>313</v>
+        <v>284</v>
       </c>
       <c r="D20" t="n">
         <v>57</v>
       </c>
       <c r="E20" t="n">
-        <v>1599573.62</v>
+        <v>1616314.45</v>
       </c>
       <c r="F20" t="n">
-        <v>1019708.41</v>
+        <v>1029973.82</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>45485</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="21">
@@ -922,13 +922,13 @@
         <v>22</v>
       </c>
       <c r="E21" t="n">
-        <v>333713.44</v>
+        <v>297558.31</v>
       </c>
       <c r="F21" t="n">
-        <v>208422.18</v>
+        <v>207925.46</v>
       </c>
       <c r="G21" s="3" t="n">
-        <v>45482</v>
+        <v>45488</v>
       </c>
     </row>
     <row r="22">
@@ -941,19 +941,19 @@
         </is>
       </c>
       <c r="C22" t="n">
-        <v>422</v>
+        <v>452</v>
       </c>
       <c r="D22" t="n">
         <v>288</v>
       </c>
       <c r="E22" t="n">
-        <v>2474394.42</v>
+        <v>2455042.19</v>
       </c>
       <c r="F22" t="n">
-        <v>1669289.44</v>
+        <v>1803686.65</v>
       </c>
       <c r="G22" s="3" t="n">
-        <v>45517</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="23">
@@ -966,16 +966,16 @@
         </is>
       </c>
       <c r="C23" t="n">
-        <v>295</v>
+        <v>326</v>
       </c>
       <c r="D23" t="n">
         <v>56</v>
       </c>
       <c r="E23" t="n">
-        <v>1786697.6</v>
+        <v>1611250.13</v>
       </c>
       <c r="F23" t="n">
-        <v>1080040.29</v>
+        <v>1094464.33</v>
       </c>
       <c r="G23" s="3" t="n">
         <v>45516</v>
@@ -991,19 +991,19 @@
         </is>
       </c>
       <c r="C24" t="n">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="D24" t="n">
         <v>24</v>
       </c>
       <c r="E24" t="n">
-        <v>311849.96</v>
+        <v>311370.81</v>
       </c>
       <c r="F24" t="n">
-        <v>239496.17</v>
+        <v>221541.41</v>
       </c>
       <c r="G24" s="3" t="n">
-        <v>45519</v>
+        <v>45512</v>
       </c>
     </row>
     <row r="25">
@@ -1016,19 +1016,19 @@
         </is>
       </c>
       <c r="C25" t="n">
-        <v>543</v>
+        <v>491</v>
       </c>
       <c r="D25" t="n">
         <v>275</v>
       </c>
       <c r="E25" t="n">
-        <v>2844092.69</v>
+        <v>2894226.23</v>
       </c>
       <c r="F25" t="n">
-        <v>2004468.78</v>
+        <v>2179298.68</v>
       </c>
       <c r="G25" s="3" t="n">
-        <v>45546</v>
+        <v>45551</v>
       </c>
     </row>
     <row r="26">
@@ -1041,19 +1041,19 @@
         </is>
       </c>
       <c r="C26" t="n">
-        <v>315</v>
+        <v>324</v>
       </c>
       <c r="D26" t="n">
         <v>78</v>
       </c>
       <c r="E26" t="n">
-        <v>1575960.27</v>
+        <v>1610552.72</v>
       </c>
       <c r="F26" t="n">
-        <v>1062314.34</v>
+        <v>1175630.19</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>45545</v>
+        <v>45548</v>
       </c>
     </row>
     <row r="27">
@@ -1066,16 +1066,16 @@
         </is>
       </c>
       <c r="C27" t="n">
-        <v>57</v>
+        <v>64</v>
       </c>
       <c r="D27" t="n">
         <v>19</v>
       </c>
       <c r="E27" t="n">
-        <v>342621.78</v>
+        <v>312787.91</v>
       </c>
       <c r="F27" t="n">
-        <v>246645.67</v>
+        <v>222722.16</v>
       </c>
       <c r="G27" s="3" t="n">
         <v>45544</v>
@@ -1091,16 +1091,16 @@
         </is>
       </c>
       <c r="C28" t="n">
-        <v>575</v>
+        <v>573</v>
       </c>
       <c r="D28" t="n">
         <v>392</v>
       </c>
       <c r="E28" t="n">
-        <v>3664834.57</v>
+        <v>3722419.23</v>
       </c>
       <c r="F28" t="n">
-        <v>2237579.53</v>
+        <v>2284301.53</v>
       </c>
       <c r="G28" s="3" t="n">
         <v>45579</v>
@@ -1116,19 +1116,19 @@
         </is>
       </c>
       <c r="C29" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="D29" t="n">
         <v>84</v>
       </c>
       <c r="E29" t="n">
-        <v>1655285.61</v>
+        <v>1698224.25</v>
       </c>
       <c r="F29" t="n">
-        <v>1108847.06</v>
+        <v>1214817.54</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>45575</v>
+        <v>45579</v>
       </c>
     </row>
     <row r="30">
@@ -1141,19 +1141,19 @@
         </is>
       </c>
       <c r="C30" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D30" t="n">
         <v>18</v>
       </c>
       <c r="E30" t="n">
-        <v>313858.84</v>
+        <v>326673.12</v>
       </c>
       <c r="F30" t="n">
-        <v>240326.24</v>
+        <v>244282.14</v>
       </c>
       <c r="G30" s="3" t="n">
-        <v>45574</v>
+        <v>45576</v>
       </c>
     </row>
     <row r="31">
@@ -1166,19 +1166,19 @@
         </is>
       </c>
       <c r="C31" t="n">
-        <v>827</v>
+        <v>732</v>
       </c>
       <c r="D31" t="n">
         <v>468</v>
       </c>
       <c r="E31" t="n">
-        <v>4379126.18</v>
+        <v>4675245.99</v>
       </c>
       <c r="F31" t="n">
-        <v>2969188.29</v>
+        <v>3016376.97</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>45607</v>
+        <v>45608</v>
       </c>
     </row>
     <row r="32">
@@ -1191,19 +1191,19 @@
         </is>
       </c>
       <c r="C32" t="n">
-        <v>335</v>
+        <v>368</v>
       </c>
       <c r="D32" t="n">
         <v>89</v>
       </c>
       <c r="E32" t="n">
-        <v>1885409.6</v>
+        <v>2101264.85</v>
       </c>
       <c r="F32" t="n">
-        <v>1289517.11</v>
+        <v>1422468.6</v>
       </c>
       <c r="G32" s="3" t="n">
-        <v>45608</v>
+        <v>45609</v>
       </c>
     </row>
     <row r="33">
@@ -1216,19 +1216,19 @@
         </is>
       </c>
       <c r="C33" t="n">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D33" t="n">
         <v>27</v>
       </c>
       <c r="E33" t="n">
-        <v>397451.64</v>
+        <v>401897.8</v>
       </c>
       <c r="F33" t="n">
-        <v>243445.99</v>
+        <v>275072.22</v>
       </c>
       <c r="G33" s="3" t="n">
-        <v>45609</v>
+        <v>45607</v>
       </c>
     </row>
     <row r="34">
@@ -1241,19 +1241,19 @@
         </is>
       </c>
       <c r="C34" t="n">
-        <v>868</v>
+        <v>877</v>
       </c>
       <c r="D34" t="n">
         <v>489</v>
       </c>
       <c r="E34" t="n">
-        <v>4964347.53</v>
+        <v>5030159.31</v>
       </c>
       <c r="F34" t="n">
-        <v>3393242.54</v>
+        <v>3397487.32</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>45637</v>
+        <v>45636</v>
       </c>
     </row>
     <row r="35">
@@ -1266,19 +1266,19 @@
         </is>
       </c>
       <c r="C35" t="n">
-        <v>405</v>
+        <v>370</v>
       </c>
       <c r="D35" t="n">
         <v>101</v>
       </c>
       <c r="E35" t="n">
-        <v>2091350.55</v>
+        <v>2282252.19</v>
       </c>
       <c r="F35" t="n">
-        <v>1391483.5</v>
+        <v>1358470.49</v>
       </c>
       <c r="G35" s="3" t="n">
-        <v>45639</v>
+        <v>45642</v>
       </c>
     </row>
     <row r="36">
@@ -1291,19 +1291,19 @@
         </is>
       </c>
       <c r="C36" t="n">
-        <v>69</v>
+        <v>71</v>
       </c>
       <c r="D36" t="n">
         <v>19</v>
       </c>
       <c r="E36" t="n">
-        <v>380562.9</v>
+        <v>377412.52</v>
       </c>
       <c r="F36" t="n">
-        <v>250062.67</v>
+        <v>257247.86</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>45635</v>
+        <v>45639</v>
       </c>
     </row>
     <row r="37">
@@ -1316,19 +1316,19 @@
         </is>
       </c>
       <c r="C37" t="n">
-        <v>886</v>
+        <v>900</v>
       </c>
       <c r="D37" t="n">
         <v>354</v>
       </c>
       <c r="E37" t="n">
-        <v>5586811.71</v>
+        <v>5644638.25</v>
       </c>
       <c r="F37" t="n">
-        <v>3534727</v>
+        <v>3578038.2</v>
       </c>
       <c r="G37" s="3" t="n">
-        <v>45672</v>
+        <v>45670</v>
       </c>
     </row>
     <row r="38">
@@ -1341,16 +1341,16 @@
         </is>
       </c>
       <c r="C38" t="n">
-        <v>429</v>
+        <v>381</v>
       </c>
       <c r="D38" t="n">
         <v>76</v>
       </c>
       <c r="E38" t="n">
-        <v>2173059.4</v>
+        <v>2194969.35</v>
       </c>
       <c r="F38" t="n">
-        <v>1575625.05</v>
+        <v>1418209.06</v>
       </c>
       <c r="G38" s="3" t="n">
         <v>45670</v>
@@ -1366,19 +1366,19 @@
         </is>
       </c>
       <c r="C39" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="D39" t="n">
         <v>25</v>
       </c>
       <c r="E39" t="n">
-        <v>369388.03</v>
+        <v>367363.28</v>
       </c>
       <c r="F39" t="n">
-        <v>245959.21</v>
+        <v>246548.66</v>
       </c>
       <c r="G39" s="3" t="n">
-        <v>45665</v>
+        <v>45671</v>
       </c>
     </row>
     <row r="40">
@@ -1391,10 +1391,10 @@
         <v>4497</v>
       </c>
       <c r="E40" t="n">
-        <v>60473978.91</v>
+        <v>60746217.88</v>
       </c>
       <c r="F40" t="n">
-        <v>39454703.22</v>
+        <v>40410242.34</v>
       </c>
     </row>
   </sheetData>
